--- a/output/errors_売上データ_202610.xlsx
+++ b/output/errors_売上データ_202610.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,27 +421,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>商品コード</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>商品名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>売上日</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>エラー内容</t>
         </is>
@@ -491,7 +479,7 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>46300</v>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -508,7 +496,7 @@
           <t>いちご</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>46303</v>
       </c>
       <c r="D4" t="n">
